--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104553_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104553_W11.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9283</v>
+        <v>3.2718</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5725</v>
+        <v>5.5149</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3559</v>
+        <v>-2.2431</v>
       </c>
       <c r="G2" t="n">
-        <v>1.201</v>
+        <v>2.4361</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5053</v>
+        <v>0.1607</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6957</v>
+        <v>2.2754</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6077</v>
+        <v>4.1253</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9311</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6765</v>
+        <v>4.0358</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4066</v>
+        <v>-1.6891</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4258</v>
+        <v>0.0713</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9808</v>
+        <v>-1.7604</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3436</v>
+        <v>-0.5285</v>
       </c>
       <c r="T2" t="n">
-        <v>2.099</v>
+        <v>-0.5601</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2447</v>
+        <v>0.0316</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6105</v>
+        <v>-0.2292</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.9497</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6105</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.075</v>
+        <v>3.2284</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4392</v>
+        <v>4.2677</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3642</v>
+        <v>-1.0393</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4509</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1587</v>
+        <v>1.2695</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2922</v>
+        <v>-0.4545</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1562</v>
+        <v>3.3342</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0968</v>
+        <v>1.2271</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0594</v>
+        <v>2.1072</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7053</v>
+        <v>-2.5193</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0619</v>
+        <v>0.0424</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7672</v>
+        <v>-2.5617</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>2.5039</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7389</v>
+        <v>0.0673</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6775</v>
+        <v>-0.156</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0614</v>
+        <v>0.2232</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2249</v>
+        <v>-0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9604</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1853</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6305</v>
+        <v>2.6561</v>
       </c>
       <c r="E4" t="n">
-        <v>3.707</v>
+        <v>2.2416</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0765</v>
+        <v>0.4145</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8193</v>
+        <v>1.1863</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2698</v>
+        <v>0.4891</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4505</v>
+        <v>0.6972</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3613</v>
+        <v>2.5741</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2397</v>
+        <v>0.9061</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1216</v>
+        <v>1.668</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.542</v>
+        <v>-1.3877</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0301</v>
+        <v>-0.4169</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.5721</v>
+        <v>-0.9708</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4952</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5232</v>
+        <v>1.0812</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.747</v>
+        <v>0.8057</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2238</v>
+        <v>0.2755</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>0.6162</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9864</v>
+        <v>2.4854</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2062</v>
+        <v>2.8852</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2198</v>
+        <v>-0.3998</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8181</v>
+        <v>-0.6955</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.37</v>
+        <v>1.4702</v>
       </c>
       <c r="J5" t="n">
-        <v>1.417</v>
+        <v>3.2503</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1185</v>
+        <v>-0.0485</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2985</v>
+        <v>3.2987</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9689</v>
+        <v>-2.4756</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3003</v>
+        <v>-0.6471</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6685</v>
+        <v>-1.8285</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7528</v>
+        <v>-0.5655</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3962</v>
+        <v>-0.3651</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3566</v>
+        <v>-0.2005</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7032</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9136</v>
+        <v>1.4963</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3183</v>
+        <v>2.7142</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4047</v>
+        <v>-1.2178</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7671</v>
+        <v>-0.5426</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7043</v>
+        <v>0.8185</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4714</v>
+        <v>-1.3611</v>
       </c>
       <c r="J6" t="n">
-        <v>3.274</v>
+        <v>1.4043</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0417</v>
+        <v>1.1064</v>
       </c>
       <c r="L6" t="n">
-        <v>3.3158</v>
+        <v>0.2979</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.507</v>
+        <v>-1.9469</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6626</v>
+        <v>-0.2879</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8444</v>
+        <v>-1.659</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1218</v>
+        <v>-1.2601</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9557</v>
+        <v>-0.8691</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1661</v>
+        <v>-0.391</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.7057</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.2503</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1367</v>
+        <v>0.876</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1451</v>
+        <v>-0.6257</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6903</v>
+        <v>-0.024</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0187</v>
+        <v>-1.1115</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.709</v>
+        <v>1.0875</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07199999999999999</v>
+        <v>1.5938</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0346</v>
+        <v>-0.1486</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>1.7425</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7622</v>
+        <v>-1.6179</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0159</v>
+        <v>-0.9629</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7463</v>
+        <v>-0.6549</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2087</v>
+        <v>-0.9941</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2087</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.3736</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2818</v>
+        <v>0.1324</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5589</v>
+        <v>-0.019</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8407</v>
+        <v>0.1513</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0276</v>
+        <v>-0.6875</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1125</v>
+        <v>0.02</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0849</v>
+        <v>-0.7075</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6158</v>
+        <v>0.0717</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1354</v>
+        <v>0.0345</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7512</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6434</v>
+        <v>-0.7592</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9771</v>
+        <v>-0.0144</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6663</v>
+        <v>-0.7447</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5322</v>
+        <v>-0.0907</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9739</v>
+        <v>-0.0907</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5583</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9577</v>
+        <v>-0.8774</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8902</v>
+        <v>1.717</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8479</v>
+        <v>-2.5944</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5507</v>
+        <v>-1.5672</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5134</v>
+        <v>-1.5299</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0373</v>
+        <v>-0.0372</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2549</v>
+        <v>1.2099</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8667</v>
+        <v>-0.8973</v>
       </c>
       <c r="L9" t="n">
-        <v>2.1216</v>
+        <v>2.1072</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8056</v>
+        <v>-2.777</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7945</v>
+        <v>-0.6957</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0302</v>
+        <v>-0.1467</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7643</v>
+        <v>-0.549</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8626</v>
+        <v>-1.8629</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6134</v>
+        <v>-2.4151</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7508</v>
+        <v>0.5522</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0924</v>
+        <v>-2.1034</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5322</v>
+        <v>-2.5413</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4398</v>
+        <v>0.4379</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.603</v>
+        <v>-0.6287</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2796</v>
+        <v>-2.2967</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4894</v>
+        <v>-1.4747</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1824</v>
+        <v>-0.1661</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8347</v>
+        <v>-0.5995</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6524</v>
+        <v>0.4335</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9179</v>
+        <v>-2.949</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5909</v>
+        <v>-1.4886</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.327</v>
+        <v>-1.4604</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.736</v>
+        <v>-1.7307</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.27</v>
+        <v>-0.2618</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4661</v>
+        <v>-1.4689</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6867</v>
+        <v>-0.7009</v>
       </c>
       <c r="K11" t="n">
-        <v>0.329</v>
+        <v>0.3275</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0157</v>
+        <v>-1.0284</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0494</v>
+        <v>-1.0298</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9966</v>
+        <v>-1.0393</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9043</v>
+        <v>-0.7877</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.2516</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1875</v>
+        <v>-7.5034</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5532</v>
+        <v>-3.8056</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6343</v>
+        <v>-3.6977</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.4529</v>
+        <v>-6.4532</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.57</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.8829</v>
+        <v>-5.8872</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.644</v>
+        <v>-3.6614</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.9962</v>
+        <v>-3.0096</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8089</v>
+        <v>-2.7918</v>
       </c>
       <c r="N12" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.8867</v>
+        <v>-2.8775</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4092</v>
+        <v>0.0801</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0907</v>
+        <v>-0.1443</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3185</v>
+        <v>0.2243</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3346999999999998</v>
+        <v>0.3280000000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>12.7981</v>
+        <v>12.4883</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.4633</v>
+        <v>-12.1602</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.8635</v>
+        <v>-7.896500000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.9318</v>
+        <v>-3.9482</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.9318</v>
+        <v>-3.9482</v>
       </c>
       <c r="J13" t="n">
-        <v>12.8252</v>
+        <v>12.5726</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2214999999999999</v>
+        <v>-0.3518</v>
       </c>
       <c r="L13" t="n">
-        <v>13.0465</v>
+        <v>12.9245</v>
       </c>
       <c r="M13" t="n">
-        <v>-20.6887</v>
+        <v>-20.469</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.7102</v>
+        <v>-3.5963</v>
       </c>
       <c r="O13" t="n">
-        <v>-16.9785</v>
+        <v>-16.8725</v>
       </c>
       <c r="P13" t="n">
-        <v>10.2074</v>
+        <v>10.2433</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.805</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0123</v>
+        <v>17.0722</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.0983</v>
+        <v>-4.1114</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.5385</v>
+        <v>-3.534</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5595999999999999</v>
+        <v>-0.5776000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>2.0888</v>
+        <v>2.092599999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>10.3161</v>
+        <v>10.2785</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.227499999999999</v>
+        <v>-8.1859</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.989</v>
+        <v>6.0821</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3197</v>
+        <v>6.2826</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3307</v>
+        <v>-0.2005</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8666</v>
+        <v>0.8711</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4978</v>
+        <v>-1.4991</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3644</v>
+        <v>2.3702</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5982</v>
+        <v>2.5702</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.1411</v>
+        <v>-2.1588</v>
       </c>
       <c r="L14" t="n">
-        <v>4.7392</v>
+        <v>4.7291</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7316</v>
+        <v>-1.6992</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6433</v>
+        <v>0.6597</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.3749</v>
+        <v>-2.3588</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3888</v>
+        <v>1.4889</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6684</v>
+        <v>0.6731</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7204</v>
+        <v>0.8157</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1135</v>
+        <v>3.4823</v>
       </c>
       <c r="E15" t="n">
-        <v>2.954</v>
+        <v>5.3271</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1595</v>
+        <v>-1.8448</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6926</v>
+        <v>4.4483</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0924</v>
+        <v>2.7919</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3998</v>
+        <v>1.6564</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9907</v>
+        <v>6.0357</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8414</v>
+        <v>3.2955</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1493</v>
+        <v>2.7402</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2981</v>
+        <v>-1.5874</v>
       </c>
       <c r="N15" t="n">
-        <v>0.251</v>
+        <v>-0.5036</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.549</v>
+        <v>-1.0838</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8065</v>
+        <v>0.2404</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8026</v>
+        <v>-0.3836</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0039</v>
+        <v>0.624</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1607</v>
+        <v>0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8709</v>
+        <v>2.2934</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7901</v>
+        <v>1.9203</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9192</v>
+        <v>0.3731</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4545</v>
+        <v>4.0901</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7965</v>
+        <v>0.0429</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6579</v>
+        <v>4.0472</v>
       </c>
       <c r="J16" t="n">
-        <v>6.0737</v>
+        <v>4.6894</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3177</v>
+        <v>0.6755</v>
       </c>
       <c r="L16" t="n">
-        <v>2.756</v>
+        <v>4.0139</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6193</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5212</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0981</v>
+        <v>0.0333</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3814</v>
+        <v>0.3414</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9739</v>
+        <v>-0.2652</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5925</v>
+        <v>0.6066</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3856</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7997</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0329</v>
+        <v>1.8836</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9266</v>
+        <v>1.6457</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8937</v>
+        <v>0.2379</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9373</v>
+        <v>0.6958</v>
       </c>
       <c r="H17" t="n">
-        <v>2.505</v>
+        <v>1.0887</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5676</v>
+        <v>-0.393</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0311</v>
+        <v>0.9796</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5385</v>
+        <v>0.8306</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4927</v>
+        <v>0.1489</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0938</v>
+        <v>-0.2838</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0335</v>
+        <v>0.2581</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0603</v>
+        <v>-0.5419</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8402</v>
+        <v>0.5748</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4548</v>
+        <v>0.5084</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3855</v>
+        <v>0.0664</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1568</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6167</v>
+        <v>0.6357</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2441</v>
+        <v>1.8307</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3727</v>
+        <v>-1.195</v>
       </c>
       <c r="G18" t="n">
-        <v>4.0878</v>
+        <v>1.951</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0389</v>
+        <v>2.5045</v>
       </c>
       <c r="I18" t="n">
-        <v>4.0489</v>
+        <v>-0.5535</v>
       </c>
       <c r="J18" t="n">
-        <v>4.7131</v>
+        <v>4.0093</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6856</v>
+        <v>2.5198</v>
       </c>
       <c r="L18" t="n">
-        <v>4.0275</v>
+        <v>1.4895</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6252</v>
+        <v>-2.0583</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.0154</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0214</v>
+        <v>-2.043</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3369</v>
+        <v>1.439</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9739</v>
+        <v>0.3968</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6369</v>
+        <v>1.0423</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5463</v>
+        <v>-1.1609</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6403</v>
+        <v>0.4736</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9867</v>
+        <v>2.5391</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.627</v>
+        <v>-2.0656</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1637</v>
+        <v>-0.1711</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9176</v>
+        <v>-1.9212</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7539</v>
+        <v>1.7501</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9042</v>
+        <v>0.8703</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.2623</v>
+        <v>-2.2795</v>
       </c>
       <c r="L19" t="n">
-        <v>3.1665</v>
+        <v>3.1498</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.068</v>
+        <v>-1.0414</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2497</v>
+        <v>-0.1277</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5565</v>
+        <v>0.0346</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6932</v>
+        <v>-0.1623</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W19" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0596</v>
+        <v>-1.842</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4629</v>
+        <v>-1.486</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5967</v>
+        <v>-0.356</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1175</v>
+        <v>1.1194</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.6783</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8045</v>
+        <v>1.7977</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5192</v>
+        <v>1.5058</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4499</v>
+        <v>1.4369</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4017</v>
+        <v>-0.3865</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6554</v>
+        <v>-0.4378</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>-0.4879</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1685</v>
+        <v>0.0501</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9316</v>
+        <v>-3.6319</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3346</v>
+        <v>-2.259</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.597</v>
+        <v>-1.3729</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5929</v>
+        <v>-0.5958</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4573</v>
+        <v>0.4621</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0503</v>
+        <v>-1.058</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5518</v>
+        <v>1.5206</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4431</v>
+        <v>0.4342</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1087</v>
+        <v>1.0864</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1447</v>
+        <v>-2.1164</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2492</v>
+        <v>0.5574</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2571</v>
+        <v>-0.1375</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5063</v>
+        <v>0.6948</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6352</v>
+        <v>-4.2487</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2084</v>
+        <v>-2.3004</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4268</v>
+        <v>-1.9483</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.394</v>
+        <v>-3.1291</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6637</v>
+        <v>0.4906</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0577</v>
+        <v>-3.6196</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3737</v>
+        <v>-1.3269</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1141</v>
+        <v>0.1034</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4878</v>
+        <v>-1.4303</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0203</v>
+        <v>-1.8022</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5496</v>
+        <v>0.3871</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5699</v>
+        <v>-2.1893</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6512</v>
+        <v>0.2265</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2994</v>
+        <v>0.0556</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3517</v>
+        <v>0.171</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.4387</v>
+        <v>0.7025</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.4387</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.691</v>
+        <v>-4.6664</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7519</v>
+        <v>-1.34</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9391</v>
+        <v>-3.3264</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1421</v>
+        <v>-1.3832</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4803</v>
+        <v>0.6662</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.6224</v>
+        <v>-2.0493</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3195</v>
+        <v>-0.3851</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1039</v>
+        <v>0.1067</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4234</v>
+        <v>-0.4917</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8225</v>
+        <v>-0.9981</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3764</v>
+        <v>0.5595</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.199</v>
+        <v>-1.5576</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0415</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2144</v>
+        <v>0.5982</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4174</v>
+        <v>0.1833</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2029</v>
+        <v>0.4149</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7071</v>
+        <v>-3.4262</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3347000000000016</v>
+        <v>0.4616999999999987</v>
       </c>
       <c r="E24" t="n">
-        <v>12.4634</v>
+        <v>12.1601</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.798</v>
+        <v>-11.6985</v>
       </c>
       <c r="G24" t="n">
-        <v>7.863599999999999</v>
+        <v>7.896499999999998</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9317</v>
+        <v>3.9483</v>
       </c>
       <c r="I24" t="n">
-        <v>3.931799999999998</v>
+        <v>3.9482</v>
       </c>
       <c r="J24" t="n">
-        <v>20.6888</v>
+        <v>20.4689</v>
       </c>
       <c r="K24" t="n">
-        <v>3.710199999999999</v>
+        <v>3.5963</v>
       </c>
       <c r="L24" t="n">
-        <v>16.9786</v>
+        <v>16.8727</v>
       </c>
       <c r="M24" t="n">
-        <v>-12.8252</v>
+        <v>-12.5726</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2214</v>
+        <v>0.3518999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-13.0468</v>
+        <v>-12.9244</v>
       </c>
       <c r="P24" t="n">
-        <v>-10.2075</v>
+        <v>-10.2434</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0126</v>
+        <v>-17.0722</v>
       </c>
       <c r="R24" t="n">
-        <v>6.804900000000001</v>
+        <v>6.8289</v>
       </c>
       <c r="S24" t="n">
-        <v>4.0981</v>
+        <v>4.9011</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5595000000000002</v>
+        <v>0.5776</v>
       </c>
       <c r="U24" t="n">
-        <v>3.5384</v>
+        <v>4.3235</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0888</v>
+        <v>-2.0926</v>
       </c>
       <c r="W24" t="n">
-        <v>8.2273</v>
+        <v>8.1859</v>
       </c>
       <c r="X24" t="n">
-        <v>-10.3162</v>
+        <v>-10.2786</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104553_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104553_W11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.1859</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104553_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-10.2786</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
